--- a/Projects/VoortoetsAGT/cases/GenericDens/GenericDens.xlsx
+++ b/Projects/VoortoetsAGT/cases/GenericDens/GenericDens.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Theo/GRWMODELS/python/mf6lab/Projects/VoortoetsAGT/cases/GenericInun/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/Theo/GRWMODELS/python/mf6lab/Projects/VoortoetsAGT/cases/GenericDens/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E56128-37D3-514F-BCCA-A4DAACBE5D9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10216DC1-CC77-264E-9DA6-1D77690243C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11860" yWindow="-26760" windowWidth="30600" windowHeight="19860" tabRatio="751" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11860" yWindow="-26760" windowWidth="30600" windowHeight="19860" tabRatio="751" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="NAM" sheetId="1" r:id="rId1"/>
@@ -7901,7 +7901,7 @@
         <v>26</v>
       </c>
       <c r="C425">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.15">
